--- a/00001/Lista_Senior_Crocco1.xlsx
+++ b/00001/Lista_Senior_Crocco1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35E7411C-FC86-4B08-B9DD-38A0B5E1B649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F1F724-BA23-4969-B446-4ED1FAEF651A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B6C1EB4E-EF18-418A-8C65-01E7780DC697}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <t>Vidal Juan José</t>
   </si>
   <si>
-    <t>Fec/Nac</t>
-  </si>
-  <si>
     <t>Club</t>
   </si>
   <si>
@@ -135,6 +132,9 @@
   </si>
   <si>
     <t>Fernandez Alberto Ramón</t>
+  </si>
+  <si>
+    <t>Clase</t>
   </si>
 </sst>
 </file>
@@ -528,8 +528,9 @@
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -543,16 +544,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -569,13 +570,13 @@
         <v>27030</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F2">
         <v>8</v>
       </c>
       <c r="G2">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -592,13 +593,13 @@
         <v>28856</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>8</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -615,13 +616,13 @@
         <v>27760</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="F4">
         <v>8</v>
       </c>
       <c r="G4">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -638,13 +639,13 @@
         <v>27760</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="F5">
         <v>8</v>
       </c>
       <c r="G5">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -661,13 +662,13 @@
         <v>28491</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F6">
         <v>8</v>
       </c>
       <c r="G6">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -675,7 +676,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2">
         <v>27412815</v>
@@ -684,13 +685,13 @@
         <v>28856</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>8</v>
       </c>
       <c r="G7">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -698,7 +699,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2">
         <v>24721291</v>
@@ -707,13 +708,13 @@
         <v>27395</v>
       </c>
       <c r="E8">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F8">
         <v>8</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -721,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2">
         <v>27984562</v>
@@ -730,13 +731,13 @@
         <v>29221</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F9">
         <v>8</v>
       </c>
       <c r="G9">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -744,7 +745,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2">
         <v>25484591</v>
@@ -753,13 +754,13 @@
         <v>27760</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F10">
         <v>8</v>
       </c>
       <c r="G10">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -776,13 +777,13 @@
         <v>28126</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>410</v>
       </c>
       <c r="F11">
         <v>8</v>
       </c>
       <c r="G11">
-        <v>410</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -790,7 +791,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2">
         <v>28367762</v>
@@ -799,13 +800,13 @@
         <v>29587</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>411</v>
       </c>
       <c r="F12">
         <v>8</v>
       </c>
       <c r="G12">
-        <v>411</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -822,13 +823,13 @@
         <v>29221</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>412</v>
       </c>
       <c r="F13">
         <v>8</v>
       </c>
       <c r="G13">
-        <v>412</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -836,7 +837,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2">
         <v>25329770</v>
@@ -845,13 +846,13 @@
         <v>27760</v>
       </c>
       <c r="E14">
-        <v>11</v>
+        <v>413</v>
       </c>
       <c r="F14">
         <v>8</v>
       </c>
       <c r="G14">
-        <v>413</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -859,7 +860,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2">
         <v>27639541</v>
@@ -868,13 +869,13 @@
         <v>28856</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>414</v>
       </c>
       <c r="F15">
         <v>8</v>
       </c>
       <c r="G15">
-        <v>414</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -891,13 +892,13 @@
         <v>28491</v>
       </c>
       <c r="E16">
-        <v>11</v>
+        <v>415</v>
       </c>
       <c r="F16">
         <v>8</v>
       </c>
       <c r="G16">
-        <v>415</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -914,13 +915,13 @@
         <v>27760</v>
       </c>
       <c r="E17">
-        <v>11</v>
+        <v>416</v>
       </c>
       <c r="F17">
         <v>8</v>
       </c>
       <c r="G17">
-        <v>416</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -937,13 +938,13 @@
         <v>28126</v>
       </c>
       <c r="E18">
-        <v>11</v>
+        <v>417</v>
       </c>
       <c r="F18">
         <v>8</v>
       </c>
       <c r="G18">
-        <v>417</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -951,7 +952,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="2">
         <v>27633235</v>
@@ -960,13 +961,13 @@
         <v>28856</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>418</v>
       </c>
       <c r="F19">
         <v>8</v>
       </c>
       <c r="G19">
-        <v>418</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -974,7 +975,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="2">
         <v>25587242</v>
@@ -983,13 +984,13 @@
         <v>27760</v>
       </c>
       <c r="E20">
-        <v>11</v>
+        <v>419</v>
       </c>
       <c r="F20">
         <v>8</v>
       </c>
       <c r="G20">
-        <v>419</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -997,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="2">
         <v>24506152</v>
@@ -1006,13 +1007,13 @@
         <v>27395</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>420</v>
       </c>
       <c r="F21">
         <v>8</v>
       </c>
       <c r="G21">
-        <v>420</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1020,7 +1021,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2">
         <v>27187987</v>
@@ -1029,13 +1030,13 @@
         <v>28856</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>421</v>
       </c>
       <c r="F22">
         <v>8</v>
       </c>
       <c r="G22">
-        <v>421</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1043,7 +1044,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2">
         <v>27615296</v>
@@ -1052,13 +1053,13 @@
         <v>29587</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>422</v>
       </c>
       <c r="F23">
         <v>8</v>
       </c>
       <c r="G23">
-        <v>422</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1066,7 +1067,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="2">
         <v>29281652</v>
@@ -1075,13 +1076,13 @@
         <v>29587</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>423</v>
       </c>
       <c r="F24">
         <v>8</v>
       </c>
       <c r="G24">
-        <v>423</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1098,13 +1099,13 @@
         <v>29221</v>
       </c>
       <c r="E25">
-        <v>11</v>
+        <v>424</v>
       </c>
       <c r="F25">
         <v>8</v>
       </c>
       <c r="G25">
-        <v>424</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1112,7 +1113,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" s="2">
         <v>28688460</v>
@@ -1121,13 +1122,13 @@
         <v>29221</v>
       </c>
       <c r="E26">
-        <v>11</v>
+        <v>425</v>
       </c>
       <c r="F26">
         <v>8</v>
       </c>
       <c r="G26">
-        <v>425</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/00001/Lista_Senior_Crocco1.xlsx
+++ b/00001/Lista_Senior_Crocco1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\David\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F1F724-BA23-4969-B446-4ED1FAEF651A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEBAF1E-CA50-4459-AE70-61574D2B7443}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B6C1EB4E-EF18-418A-8C65-01E7780DC697}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="4515" xr2:uid="{B6C1EB4E-EF18-418A-8C65-01E7780DC697}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -44,9 +33,6 @@
     <t>N°</t>
   </si>
   <si>
-    <t>Apellido - Nombre</t>
-  </si>
-  <si>
     <t>DNI</t>
   </si>
   <si>
@@ -86,12 +72,6 @@
     <t>Club</t>
   </si>
   <si>
-    <t>Categoria</t>
-  </si>
-  <si>
-    <t>Carnet</t>
-  </si>
-  <si>
     <t>Vargas Juan</t>
   </si>
   <si>
@@ -135,13 +115,22 @@
   </si>
   <si>
     <t>Clase</t>
+  </si>
+  <si>
+    <t>Apellido y Nombre</t>
+  </si>
+  <si>
+    <t>N° Carnet</t>
+  </si>
+  <si>
+    <t>Cat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,46 +511,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF58F495-E8FE-4B48-AFF3-EF57A0211A02}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="27.33203125" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="27.375" defaultRowHeight="13.15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="13.15" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="13.15" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2">
         <v>23948998</v>
@@ -579,12 +568,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="13.15" customHeight="1">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2">
         <v>27126946</v>
@@ -602,12 +591,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="13.15" customHeight="1">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2">
         <v>25089498</v>
@@ -625,12 +614,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="13.15" customHeight="1">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2">
         <v>25585136</v>
@@ -648,12 +637,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="13.15" customHeight="1">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2">
         <v>27792911</v>
@@ -671,12 +660,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="13.15" customHeight="1">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>27412815</v>
@@ -694,12 +683,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="13.15" customHeight="1">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2">
         <v>24721291</v>
@@ -717,12 +706,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="13.15" customHeight="1">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2">
         <v>27984562</v>
@@ -740,12 +729,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="13.15" customHeight="1">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2">
         <v>25484591</v>
@@ -763,12 +752,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="13.15" customHeight="1">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2">
         <v>25842641</v>
@@ -786,12 +775,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="13.15" customHeight="1">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C12" s="2">
         <v>28367762</v>
@@ -809,12 +798,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="13.15" customHeight="1">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2">
         <v>27984591</v>
@@ -832,12 +821,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="13.15" customHeight="1">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14" s="2">
         <v>25329770</v>
@@ -855,12 +844,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="13.15" customHeight="1">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C15" s="2">
         <v>27639541</v>
@@ -878,12 +867,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="13.15" customHeight="1">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2">
         <v>26386556</v>
@@ -901,12 +890,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="13.15" customHeight="1">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="2">
         <v>25447563</v>
@@ -924,12 +913,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="13.15" customHeight="1">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="2">
         <v>27530233</v>
@@ -947,12 +936,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="13.15" customHeight="1">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C19" s="2">
         <v>27633235</v>
@@ -970,12 +959,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="13.15" customHeight="1">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C20" s="2">
         <v>25587242</v>
@@ -993,12 +982,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="13.15" customHeight="1">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C21" s="2">
         <v>24506152</v>
@@ -1016,12 +1005,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="13.15" customHeight="1">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C22" s="2">
         <v>27187987</v>
@@ -1039,12 +1028,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="13.15" customHeight="1">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C23" s="2">
         <v>27615296</v>
@@ -1062,12 +1051,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="13.15" customHeight="1">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C24" s="2">
         <v>29281652</v>
@@ -1085,12 +1074,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="13.15" customHeight="1">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" s="2">
         <v>26386568</v>
@@ -1108,12 +1097,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="13.15" customHeight="1">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2">
         <v>28688460</v>
